--- a/clustering/subcluster_validation.xlsx
+++ b/clustering/subcluster_validation.xlsx
@@ -471,16 +471,16 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0857689296445576</v>
+        <v>0.08907647320480729</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8810107244543943</v>
+        <v>0.8691051920443705</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7570228091236494</v>
+        <v>0.7313805522208884</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9411682361704347</v>
+        <v>0.9359265390783954</v>
       </c>
     </row>
     <row r="3">
@@ -494,16 +494,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1253938726259034</v>
+        <v>0.1086000656691323</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8294862244753252</v>
+        <v>0.7655126405577777</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9335414165666266</v>
+        <v>0.8916686674669867</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9421920851597723</v>
+        <v>0.8843488459120704</v>
       </c>
     </row>
     <row r="4">
@@ -517,16 +517,16 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1066199881089169</v>
+        <v>0.1171973281897905</v>
       </c>
       <c r="E4" t="n">
-        <v>0.773724997668206</v>
+        <v>0.8472453731468708</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8973349339735894</v>
+        <v>0.9396878751500599</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8906402889818951</v>
+        <v>0.9460220255853413</v>
       </c>
     </row>
     <row r="5">
@@ -540,16 +540,16 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1666040311202699</v>
+        <v>0.1287992097833589</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6211334390096492</v>
+        <v>0.6023569399840163</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9709963985594238</v>
+        <v>0.9435294117647057</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9461477730772768</v>
+        <v>0.9706911278707716</v>
       </c>
     </row>
     <row r="6">
@@ -563,16 +563,16 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1298460753464768</v>
+        <v>0.1475851587633744</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5895025591962051</v>
+        <v>0.7093108022058517</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9447779111644657</v>
+        <v>0.9732052821128452</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9695909216014744</v>
+        <v>0.9556366471546732</v>
       </c>
     </row>
     <row r="7">
@@ -586,16 +586,16 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07845241233594856</v>
+        <v>0.07513133724588279</v>
       </c>
       <c r="E7" t="n">
-        <v>0.852754596060079</v>
+        <v>0.8647883017034811</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9059783913565426</v>
+        <v>0.9124129651860744</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9758195851438102</v>
+        <v>0.9759887812174456</v>
       </c>
     </row>
     <row r="8">
@@ -609,16 +609,16 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06238681286504759</v>
+        <v>0.0582402328692117</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9589197685817341</v>
+        <v>0.9639010321871334</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9282593037214885</v>
+        <v>0.9257623049219688</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9821576826316816</v>
+        <v>0.9833255510105042</v>
       </c>
     </row>
     <row r="9">
@@ -632,16 +632,16 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1118465099607808</v>
+        <v>0.07738680607815142</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8159585967475373</v>
+        <v>0.9491859108478805</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9105882352941176</v>
+        <v>0.9393997599039615</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9127796875254531</v>
+        <v>0.9834627499179067</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1096074670639612</v>
+        <v>0.09747801192522322</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8474745146578344</v>
+        <v>0.8834392630267112</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7655702280912365</v>
+        <v>0.8036014405762305</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9648245823408281</v>
+        <v>0.9700142326569631</v>
       </c>
     </row>
     <row r="11">
@@ -678,16 +678,16 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08405063525084222</v>
+        <v>0.1130511747277975</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9394506724184628</v>
+        <v>0.8164074085483586</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9420888355342137</v>
+        <v>0.9140456182472988</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9822879782264887</v>
+        <v>0.9130090743687043</v>
       </c>
     </row>
   </sheetData>

--- a/clustering/subcluster_validation.xlsx
+++ b/clustering/subcluster_validation.xlsx
@@ -471,16 +471,16 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08907647320480729</v>
+        <v>0.1170752425142875</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8691051920443705</v>
+        <v>0.8483439264796244</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7313805522208884</v>
+        <v>0.9355582232893157</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9359265390783954</v>
+        <v>0.9456752927111909</v>
       </c>
     </row>
     <row r="3">
@@ -494,16 +494,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1086000656691323</v>
+        <v>0.1082150235114922</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7655126405577777</v>
+        <v>0.7667893609487038</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8916686674669867</v>
+        <v>0.8957022809123649</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8843488459120704</v>
+        <v>0.8844892862329677</v>
       </c>
     </row>
     <row r="4">
@@ -517,16 +517,16 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1171973281897905</v>
+        <v>0.08962363626157301</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8472453731468708</v>
+        <v>0.8677562591151396</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9396878751500599</v>
+        <v>0.7168787515006002</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9460220255853413</v>
+        <v>0.9351653824322173</v>
       </c>
     </row>
     <row r="5">
@@ -540,16 +540,16 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1287992097833589</v>
+        <v>0.1289921488079956</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6023569399840163</v>
+        <v>0.6055211064238641</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9435294117647057</v>
+        <v>0.9452581032412964</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9706911278707716</v>
+        <v>0.9709745728216159</v>
       </c>
     </row>
     <row r="6">
@@ -563,16 +563,16 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1475851587633744</v>
+        <v>0.1436580774169303</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7093108022058517</v>
+        <v>0.7305712204821815</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9732052821128452</v>
+        <v>0.9740696278511404</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9556366471546732</v>
+        <v>0.9559460842578057</v>
       </c>
     </row>
     <row r="7">
@@ -586,16 +586,16 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07513133724588279</v>
+        <v>0.07597097570237224</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8647883017034811</v>
+        <v>0.8599966865658379</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9124129651860744</v>
+        <v>0.9071308523409364</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9759887812174456</v>
+        <v>0.9753333541049379</v>
       </c>
     </row>
     <row r="8">
@@ -609,16 +609,16 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0582402328692117</v>
+        <v>0.05797511160015081</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9639010321871334</v>
+        <v>0.9639474125245594</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9257623049219688</v>
+        <v>0.9231692677070827</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9833255510105042</v>
+        <v>0.9833204509229431</v>
       </c>
     </row>
     <row r="9">
@@ -632,16 +632,16 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07738680607815142</v>
+        <v>0.113683350306907</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9491859108478805</v>
+        <v>0.8133392753207229</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9393997599039615</v>
+        <v>0.9130852340936374</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9834627499179067</v>
+        <v>0.9113365921270679</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,16 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.09747801192522322</v>
+        <v>0.09790300214108776</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8834392630267112</v>
+        <v>0.8799964296016228</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8036014405762305</v>
+        <v>0.8030252100840336</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9700142326569631</v>
+        <v>0.9694938514233622</v>
       </c>
     </row>
     <row r="11">
@@ -678,16 +678,16 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1130511747277975</v>
+        <v>0.07672555471736636</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8164074085483586</v>
+        <v>0.9497252807761979</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9140456182472988</v>
+        <v>0.9430492196878751</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9130090743687043</v>
+        <v>0.9836173744175832</v>
       </c>
     </row>
   </sheetData>

--- a/clustering/subcluster_validation.xlsx
+++ b/clustering/subcluster_validation.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,16 +471,16 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1170752425142875</v>
+        <v>0.08962363794186723</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8483439264796244</v>
+        <v>0.867756258279535</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9355582232893157</v>
+        <v>0.7168787515006002</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9456752927111909</v>
+        <v>0.9351653808896341</v>
       </c>
     </row>
     <row r="3">
@@ -494,16 +494,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1082150235114922</v>
+        <v>0.1082150224805601</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7667893609487038</v>
+        <v>0.7667893620626833</v>
       </c>
       <c r="F3" t="n">
         <v>0.8957022809123649</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8844892862329677</v>
+        <v>0.8844892857647731</v>
       </c>
     </row>
     <row r="4">
@@ -517,16 +517,16 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08962363626157301</v>
+        <v>0.1170752438419326</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8677562591151396</v>
+        <v>0.8483439224190171</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7168787515006002</v>
+        <v>0.9355582232893157</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9351653824322173</v>
+        <v>0.9456752924425912</v>
       </c>
     </row>
     <row r="5">
@@ -540,16 +540,16 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1289921488079956</v>
+        <v>0.1436580763861961</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6055211064238641</v>
+        <v>0.7305712248608096</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9452581032412964</v>
+        <v>0.9740696278511404</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9709745728216159</v>
+        <v>0.9559460844212535</v>
       </c>
     </row>
     <row r="6">
@@ -563,16 +563,16 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1436580774169303</v>
+        <v>0.1289921502776568</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7305712204821815</v>
+        <v>0.6055210952157676</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9740696278511404</v>
+        <v>0.9452581032412964</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9559460842578057</v>
+        <v>0.9709745726717519</v>
       </c>
     </row>
     <row r="7">
@@ -586,16 +586,16 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07597097570237224</v>
+        <v>0.07597097558467218</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8599966865658379</v>
+        <v>0.8599966813738533</v>
       </c>
       <c r="F7" t="n">
         <v>0.9071308523409364</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9753333541049379</v>
+        <v>0.9753333571043648</v>
       </c>
     </row>
     <row r="8">
@@ -609,16 +609,16 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05797511160015081</v>
+        <v>0.05797511075874925</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9639474125245594</v>
+        <v>0.9639474132032053</v>
       </c>
       <c r="F8" t="n">
         <v>0.9231692677070827</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9833204509229431</v>
+        <v>0.9833204511098125</v>
       </c>
     </row>
     <row r="9">
@@ -632,16 +632,16 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.113683350306907</v>
+        <v>0.09038797542020788</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8133392753207229</v>
+        <v>0.8915698816055511</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9130852340936374</v>
+        <v>0.8156062424969988</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9113365921270679</v>
+        <v>0.9670437413267302</v>
       </c>
     </row>
     <row r="10">
@@ -655,39 +655,16 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.09790300214108776</v>
+        <v>0.08466178446046518</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8799964296016228</v>
+        <v>0.9308020961634722</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8030252100840336</v>
+        <v>0.9467947178871549</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9694938514233622</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.07672555471736636</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.9497252807761979</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.9430492196878751</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.9836173744175832</v>
+        <v>0.9780926467671515</v>
       </c>
     </row>
   </sheetData>

--- a/clustering/subcluster_validation.xlsx
+++ b/clustering/subcluster_validation.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,16 +471,16 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08962363794186723</v>
+        <v>0.08414467393200989</v>
       </c>
       <c r="E2" t="n">
-        <v>0.867756258279535</v>
+        <v>0.8804368233845343</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7168787515006002</v>
+        <v>0.7113085234093637</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9351653808896341</v>
+        <v>0.940797972206952</v>
       </c>
     </row>
     <row r="3">
@@ -494,16 +494,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1082150224805601</v>
+        <v>0.1064487754484439</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7667893620626833</v>
+        <v>0.7770335285008199</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8957022809123649</v>
+        <v>0.8958943577430971</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8844892857647731</v>
+        <v>0.8891606244536595</v>
       </c>
     </row>
     <row r="4">
@@ -517,16 +517,16 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1170752438419326</v>
+        <v>0.1193174461087964</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8483439224190171</v>
+        <v>0.84363780562997</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9355582232893157</v>
+        <v>0.9026170468187275</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9456752924425912</v>
+        <v>0.9506586395331509</v>
       </c>
     </row>
     <row r="5">
@@ -540,16 +540,16 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1436580763861961</v>
+        <v>0.09061687748482661</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7305712248608096</v>
+        <v>0.80180455835145</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9740696278511404</v>
+        <v>0.9604321728691476</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9559460844212535</v>
+        <v>0.966881881820442</v>
       </c>
     </row>
     <row r="6">
@@ -563,16 +563,16 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1289921502776568</v>
+        <v>0.1365131353478551</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6055210952157676</v>
+        <v>0.7583381658331114</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9452581032412964</v>
+        <v>0.9706122448979591</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9709745726717519</v>
+        <v>0.9562670454737177</v>
       </c>
     </row>
     <row r="7">
@@ -586,16 +586,16 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07597097558467218</v>
+        <v>0.05566925576289834</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8599966813738533</v>
+        <v>0.9282380055087845</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9071308523409364</v>
+        <v>0.907611044417767</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9753333571043648</v>
+        <v>0.9809994895104892</v>
       </c>
     </row>
     <row r="8">
@@ -609,16 +609,16 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05797511075874925</v>
+        <v>0.07194756290937568</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9639474132032053</v>
+        <v>0.9455647562677874</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9231692677070827</v>
+        <v>0.9307563025210084</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9833204511098125</v>
+        <v>0.9787167269409413</v>
       </c>
     </row>
     <row r="9">
@@ -632,16 +632,16 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.09038797542020788</v>
+        <v>0.1115643604186725</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8915698816055511</v>
+        <v>0.8195768976393046</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8156062424969988</v>
+        <v>0.9162545018007202</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9670437413267302</v>
+        <v>0.9115872645258486</v>
       </c>
     </row>
     <row r="10">
@@ -655,16 +655,39 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.08466178446046518</v>
+        <v>0.08378214925304331</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9308020961634722</v>
+        <v>0.9402296109502734</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9467947178871549</v>
+        <v>0.9435294117647057</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9780926467671515</v>
+        <v>0.9786246847995599</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.09553632028480361</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.8854045041967674</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8229051620648258</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9659311384422858</v>
       </c>
     </row>
   </sheetData>

--- a/clustering/subcluster_validation.xlsx
+++ b/clustering/subcluster_validation.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,16 +471,16 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08414467393200989</v>
+        <v>0.3908800902175323</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8804368233845343</v>
+        <v>0.7945450790896549</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7113085234093637</v>
+        <v>0.8121488595438175</v>
       </c>
       <c r="G2" t="n">
-        <v>0.940797972206952</v>
+        <v>0.9223980229593314</v>
       </c>
     </row>
     <row r="3">
@@ -494,16 +494,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1064487754484439</v>
+        <v>0.3099997486980506</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7770335285008199</v>
+        <v>0.8781041917398295</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8958943577430971</v>
+        <v>0.9758943577430972</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8891606244536595</v>
+        <v>0.9529596769606465</v>
       </c>
     </row>
     <row r="4">
@@ -511,22 +511,22 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
         <v>0</v>
       </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
       <c r="D4" t="n">
-        <v>0.1193174461087964</v>
+        <v>0.2157791787069614</v>
       </c>
       <c r="E4" t="n">
-        <v>0.84363780562997</v>
+        <v>0.9371117936833578</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9026170468187275</v>
+        <v>0.9588955582232893</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9506586395331509</v>
+        <v>0.9842605006012564</v>
       </c>
     </row>
     <row r="5">
@@ -537,19 +537,19 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09061687748482661</v>
+        <v>0.3128881155914726</v>
       </c>
       <c r="E5" t="n">
-        <v>0.80180455835145</v>
+        <v>0.8537883554301291</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9604321728691476</v>
+        <v>0.9467947178871549</v>
       </c>
       <c r="G5" t="n">
-        <v>0.966881881820442</v>
+        <v>0.9603590743745045</v>
       </c>
     </row>
     <row r="6">
@@ -557,22 +557,22 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1365131353478551</v>
+        <v>0.2253295142845625</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7583381658331114</v>
+        <v>0.9385711201077689</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9706122448979591</v>
+        <v>0.9577430972388956</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9562670454737177</v>
+        <v>0.9766162870954797</v>
       </c>
     </row>
     <row r="7">
@@ -583,111 +583,19 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05566925576289834</v>
+        <v>0.2951246970900211</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9282380055087845</v>
+        <v>0.8848869991578254</v>
       </c>
       <c r="F7" t="n">
-        <v>0.907611044417767</v>
+        <v>0.8641056422569027</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9809994895104892</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.07194756290937568</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.9455647562677874</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.9307563025210084</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.9787167269409413</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1115643604186725</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.8195768976393046</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.9162545018007202</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.9115872645258486</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.08378214925304331</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.9402296109502734</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.9435294117647057</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.9786246847995599</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.09553632028480361</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.8854045041967674</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.8229051620648258</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.9659311384422858</v>
+        <v>0.9596716651866897</v>
       </c>
     </row>
   </sheetData>

--- a/clustering/subcluster_validation.xlsx
+++ b/clustering/subcluster_validation.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,16 +471,16 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3908800902175323</v>
+        <v>0.3193356972815224</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7945450790896549</v>
+        <v>0.8702646088637457</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8121488595438175</v>
+        <v>0.9753181272509003</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9223980229593314</v>
+        <v>0.9497443715065357</v>
       </c>
     </row>
     <row r="3">
@@ -494,16 +494,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3099997486980506</v>
+        <v>0.3932036803167929</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8781041917398295</v>
+        <v>0.7918954445636512</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9758943577430972</v>
+        <v>0.8195438175270108</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9529596769606465</v>
+        <v>0.9213701008866887</v>
       </c>
     </row>
     <row r="4">
@@ -517,16 +517,16 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2157791787069614</v>
+        <v>0.3130080768595227</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9371117936833578</v>
+        <v>0.8528224910872011</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9588955582232893</v>
+        <v>0.9489075630252101</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9842605006012564</v>
+        <v>0.9607304226048151</v>
       </c>
     </row>
     <row r="5">
@@ -540,16 +540,16 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3128881155914726</v>
+        <v>0.2144725280303744</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8537883554301291</v>
+        <v>0.9378979747544799</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9467947178871549</v>
+        <v>0.9486194477791116</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9603590743745045</v>
+        <v>0.9845603788846315</v>
       </c>
     </row>
     <row r="6">
@@ -563,16 +563,16 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2253295142845625</v>
+        <v>0.2126109705624795</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9385711201077689</v>
+        <v>0.9478015794887615</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9577430972388956</v>
+        <v>0.956782713085234</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9766162870954797</v>
+        <v>0.9783011895484264</v>
       </c>
     </row>
     <row r="7">
@@ -586,16 +586,39 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2951246970900211</v>
+        <v>0.4685939657912299</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8848869991578254</v>
+        <v>0.6726969928261706</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8641056422569027</v>
+        <v>0.8890756302521008</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9596716651866897</v>
+        <v>0.8859408780411094</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2508013305041116</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9272488433726116</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9168307322929171</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9688230454178981</v>
       </c>
     </row>
   </sheetData>
